--- a/pcor-cm-erq-s-linkids.xlsx
+++ b/pcor-cm-erq-s-linkids.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>ERQ-S: Dictionary-Variablen-IDs → FHIR-linkIds</t>
+    <t>ERQ-6: Dictionary-Variablen-IDs → FHIR-linkIds</t>
   </si>
   <si>
     <t>Status</t>
@@ -84,13 +84,13 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Bildet die sequenziellen Variablen-IDs des PCOR-MII Item Level Dictionary (erq1–erq6) auf die linkIds des ERQ-S-Questionnaire ab, die den normativen ERQ-Itemnummern entsprechen (1, 2, 3, 6, 8, 9). Erforderlich, weil drei IDs abweichen und `erq6` in beiden Systemen existiert, dort aber verschiedene Items bezeichnet — ein Mapping über Namensgleichheit führt zu einer stillen Fehlzuordnung.</t>
+    <t>Bildet die sequenziellen Variablen-IDs des PCOR-MII Item Level Dictionary (erq1–erq6) auf die linkIds des ERQ-6-Questionnaire ab, die den Original-ERQ-Itemnummern entsprechen (1, 2, 3, 6, 8, 9). Erforderlich, weil drei IDs abweichen und `erq6` in beiden Systemen existiert, dort aber verschiedene Items bezeichnet — ein Mapping über Namensgleichheit führt zu einer stillen Fehlzuordnung. Hinweis: Die Id dieser ConceptMap enthält historisch „erq-s“; der Bogen ist jedoch nicht der ERQ-S (siehe [ERQ-6](ERQ-6.html)).</t>
   </si>
   <si>
     <t>Purpose</t>
   </si>
   <si>
-    <t>Lesehilfe für die Übernahme von Studiendaten, die unter den Variablennamen des Item Level Dictionary erhoben wurden, in QuestionnaireResponses zum ERQ-S-Questionnaire.</t>
+    <t>Lesehilfe für die Übernahme von Studiendaten, die unter den Variablennamen des Item Level Dictionary erhoben wurden, in QuestionnaireResponses zum ERQ-6-Questionnaire.</t>
   </si>
   <si>
     <t>Copyright</t>
